--- a/lub_backend/data/Fleet_Luboil_Config.xlsx
+++ b/lub_backend/data/Fleet_Luboil_Config.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\Ozellar_project\Aepms-backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\lub_backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C89E6CC-49B1-4C4E-B5D5-907634A3FF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9434F80A-E6AA-4622-A120-E01D2408E70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F8E72700-DAC3-3D4E-948A-50F093560C81}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="262">
   <si>
     <t>Equipment</t>
   </si>
@@ -817,6 +817,9 @@
   </si>
   <si>
     <t>GCL Saraswati-9644500</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 940093P09</t>
   </si>
 </sst>
 </file>
@@ -1612,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>46</v>
+        <v>261</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>46</v>

--- a/lub_backend/data/Fleet_Luboil_Config.xlsx
+++ b/lub_backend/data/Fleet_Luboil_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\lub_backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9434F80A-E6AA-4622-A120-E01D2408E70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBA14F7-84A1-412B-A71F-0DDB5DE3503F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F8E72700-DAC3-3D4E-948A-50F093560C81}"/>
   </bookViews>
@@ -378,448 +378,448 @@
     <t>419853P16</t>
   </si>
   <si>
+    <t>419853P18</t>
+  </si>
+  <si>
+    <t>419853P02</t>
+  </si>
+  <si>
+    <t>419853A01</t>
+  </si>
+  <si>
+    <t>419853A02</t>
+  </si>
+  <si>
+    <t>419853A03</t>
+  </si>
+  <si>
+    <t>419853A04</t>
+  </si>
+  <si>
+    <t>419853D01</t>
+  </si>
+  <si>
+    <t>419853D02</t>
+  </si>
+  <si>
+    <t>419853D03</t>
+  </si>
+  <si>
+    <t>419853D04</t>
+  </si>
+  <si>
+    <t>419853D05</t>
+  </si>
+  <si>
+    <t>419853D06</t>
+  </si>
+  <si>
+    <t>419853D07</t>
+  </si>
+  <si>
+    <t>934587P01</t>
+  </si>
+  <si>
+    <t>934587P11</t>
+  </si>
+  <si>
+    <t>934587P12</t>
+  </si>
+  <si>
+    <t>934587P13</t>
+  </si>
+  <si>
+    <t>934587P14</t>
+  </si>
+  <si>
+    <t>934587P15</t>
+  </si>
+  <si>
+    <t>934587P16</t>
+  </si>
+  <si>
+    <t>934587P18</t>
+  </si>
+  <si>
+    <t>934587P02</t>
+  </si>
+  <si>
+    <t>934587A01</t>
+  </si>
+  <si>
+    <t>934587A02</t>
+  </si>
+  <si>
+    <t>934587A03</t>
+  </si>
+  <si>
+    <t>934587A04</t>
+  </si>
+  <si>
+    <t>934587D01</t>
+  </si>
+  <si>
+    <t>934587D02</t>
+  </si>
+  <si>
+    <t>934587D07</t>
+  </si>
+  <si>
+    <t>940097P01</t>
+  </si>
+  <si>
+    <t>940097P03</t>
+  </si>
+  <si>
+    <t>940097P04</t>
+  </si>
+  <si>
+    <t>940097P05</t>
+  </si>
+  <si>
+    <t>940097P06</t>
+  </si>
+  <si>
+    <t>940097P07</t>
+  </si>
+  <si>
+    <t>940097P08</t>
+  </si>
+  <si>
+    <t>940097P02</t>
+  </si>
+  <si>
+    <t>940097A01</t>
+  </si>
+  <si>
+    <t>940097A02</t>
+  </si>
+  <si>
+    <t>940097A03</t>
+  </si>
+  <si>
+    <t>940097A04</t>
+  </si>
+  <si>
+    <t>940097D01</t>
+  </si>
+  <si>
+    <t>940097D05</t>
+  </si>
+  <si>
+    <t>940097D06</t>
+  </si>
+  <si>
+    <t>940097D04</t>
+  </si>
+  <si>
+    <t>940097D08</t>
+  </si>
+  <si>
+    <t>940097D03</t>
+  </si>
+  <si>
+    <t>940096P01</t>
+  </si>
+  <si>
+    <t>940096P03</t>
+  </si>
+  <si>
+    <t>940096P04</t>
+  </si>
+  <si>
+    <t>940096P05</t>
+  </si>
+  <si>
+    <t>940096P06</t>
+  </si>
+  <si>
+    <t>940096P07</t>
+  </si>
+  <si>
+    <t>940096P08</t>
+  </si>
+  <si>
+    <t>940096P02</t>
+  </si>
+  <si>
+    <t>940096A01</t>
+  </si>
+  <si>
+    <t>940096A02</t>
+  </si>
+  <si>
+    <t>940096A03</t>
+  </si>
+  <si>
+    <t>940096A04</t>
+  </si>
+  <si>
+    <t>940096D01</t>
+  </si>
+  <si>
+    <t>940096D05</t>
+  </si>
+  <si>
+    <t>940096D06</t>
+  </si>
+  <si>
+    <t>940096D04</t>
+  </si>
+  <si>
+    <t>940096D07</t>
+  </si>
+  <si>
+    <t>940096D03</t>
+  </si>
+  <si>
+    <t>940093P01</t>
+  </si>
+  <si>
+    <t>940093P03</t>
+  </si>
+  <si>
+    <t>940093P04</t>
+  </si>
+  <si>
+    <t>940093P05</t>
+  </si>
+  <si>
+    <t>940093P06</t>
+  </si>
+  <si>
+    <t>940093P07</t>
+  </si>
+  <si>
+    <t>940093P08</t>
+  </si>
+  <si>
+    <t>940093P02</t>
+  </si>
+  <si>
+    <t>940093A01</t>
+  </si>
+  <si>
+    <t>940093A02</t>
+  </si>
+  <si>
+    <t>940093A03</t>
+  </si>
+  <si>
+    <t>940093A04</t>
+  </si>
+  <si>
+    <t>940093D01</t>
+  </si>
+  <si>
+    <t>940093D05</t>
+  </si>
+  <si>
+    <t>940093D06</t>
+  </si>
+  <si>
+    <t>940093D04</t>
+  </si>
+  <si>
+    <t>940093D07</t>
+  </si>
+  <si>
+    <t>940093D03</t>
+  </si>
+  <si>
+    <t>943611P01</t>
+  </si>
+  <si>
+    <t>943611P11</t>
+  </si>
+  <si>
+    <t>943611P12</t>
+  </si>
+  <si>
+    <t>943611P13</t>
+  </si>
+  <si>
+    <t>943611P14</t>
+  </si>
+  <si>
+    <t>943611P15</t>
+  </si>
+  <si>
+    <t>943611P16</t>
+  </si>
+  <si>
+    <t>943611P02</t>
+  </si>
+  <si>
+    <t>943611A01</t>
+  </si>
+  <si>
+    <t>943611A02</t>
+  </si>
+  <si>
+    <t>943611A03</t>
+  </si>
+  <si>
+    <t>943611A04</t>
+  </si>
+  <si>
+    <t>943611D01</t>
+  </si>
+  <si>
+    <t>943611D02</t>
+  </si>
+  <si>
+    <t>943611D08</t>
+  </si>
+  <si>
+    <t>940094P01</t>
+  </si>
+  <si>
+    <t>940094P11</t>
+  </si>
+  <si>
+    <t>940094P12</t>
+  </si>
+  <si>
+    <t>940094P13</t>
+  </si>
+  <si>
+    <t>940094P14</t>
+  </si>
+  <si>
+    <t>940094P15</t>
+  </si>
+  <si>
+    <t>940094P16</t>
+  </si>
+  <si>
+    <t>940094P17</t>
+  </si>
+  <si>
+    <t>940094P18</t>
+  </si>
+  <si>
+    <t>940094P02</t>
+  </si>
+  <si>
+    <t>940094A01</t>
+  </si>
+  <si>
+    <t>940094A02</t>
+  </si>
+  <si>
+    <t>940094A03</t>
+  </si>
+  <si>
+    <t>940094A04</t>
+  </si>
+  <si>
+    <t>940094D01</t>
+  </si>
+  <si>
+    <t>940094D05</t>
+  </si>
+  <si>
+    <t>940094D06</t>
+  </si>
+  <si>
+    <t>940094D02</t>
+  </si>
+  <si>
+    <t>940094D07</t>
+  </si>
+  <si>
+    <t>940094D04</t>
+  </si>
+  <si>
+    <t>940095P01</t>
+  </si>
+  <si>
+    <t>940095P03</t>
+  </si>
+  <si>
+    <t>940095P04</t>
+  </si>
+  <si>
+    <t>940095P05</t>
+  </si>
+  <si>
+    <t>940095P06</t>
+  </si>
+  <si>
+    <t>940095P07</t>
+  </si>
+  <si>
+    <t>940095P08</t>
+  </si>
+  <si>
+    <t>940095P02</t>
+  </si>
+  <si>
+    <t>940095A01</t>
+  </si>
+  <si>
+    <t>940095A02</t>
+  </si>
+  <si>
+    <t>940095A03</t>
+  </si>
+  <si>
+    <t>940095A04</t>
+  </si>
+  <si>
+    <t>940095D01</t>
+  </si>
+  <si>
+    <t>940095D03</t>
+  </si>
+  <si>
+    <t>940095D04</t>
+  </si>
+  <si>
+    <t>940095D02</t>
+  </si>
+  <si>
+    <t>940095D07</t>
+  </si>
+  <si>
+    <t>940095D06</t>
+  </si>
+  <si>
+    <t>GCL Yamuna-9481219</t>
+  </si>
+  <si>
+    <t>GCL Tapi-9481659</t>
+  </si>
+  <si>
+    <t>GCL Sabarmati-9481661</t>
+  </si>
+  <si>
+    <t>GCL Ganga-9481697</t>
+  </si>
+  <si>
+    <t>AM Umang-9792058</t>
+  </si>
+  <si>
+    <t>AM Tarang-9832913</t>
+  </si>
+  <si>
+    <t>AM Kirti-9832925</t>
+  </si>
+  <si>
+    <t>GCL Narmadha-9481685</t>
+  </si>
+  <si>
+    <t>GCL Saraswati-9644500</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 940093P09</t>
+  </si>
+  <si>
     <t>419853P17</t>
   </si>
   <si>
-    <t>419853P18</t>
-  </si>
-  <si>
-    <t>419853P02</t>
-  </si>
-  <si>
-    <t>419853A01</t>
-  </si>
-  <si>
-    <t>419853A02</t>
-  </si>
-  <si>
-    <t>419853A03</t>
-  </si>
-  <si>
-    <t>419853A04</t>
-  </si>
-  <si>
-    <t>419853D01</t>
-  </si>
-  <si>
-    <t>419853D02</t>
-  </si>
-  <si>
-    <t>419853D03</t>
-  </si>
-  <si>
-    <t>419853D04</t>
-  </si>
-  <si>
-    <t>419853D05</t>
-  </si>
-  <si>
-    <t>419853D06</t>
-  </si>
-  <si>
-    <t>419853D07</t>
-  </si>
-  <si>
-    <t>934587P01</t>
-  </si>
-  <si>
-    <t>934587P11</t>
-  </si>
-  <si>
-    <t>934587P12</t>
-  </si>
-  <si>
-    <t>934587P13</t>
-  </si>
-  <si>
-    <t>934587P14</t>
-  </si>
-  <si>
-    <t>934587P15</t>
-  </si>
-  <si>
-    <t>934587P16</t>
-  </si>
-  <si>
-    <t>934587P17</t>
-  </si>
-  <si>
-    <t>934587P18</t>
-  </si>
-  <si>
-    <t>934587P02</t>
-  </si>
-  <si>
-    <t>934587A01</t>
-  </si>
-  <si>
-    <t>934587A02</t>
-  </si>
-  <si>
-    <t>934587A03</t>
-  </si>
-  <si>
-    <t>934587A04</t>
-  </si>
-  <si>
-    <t>934587D01</t>
-  </si>
-  <si>
-    <t>934587D02</t>
-  </si>
-  <si>
-    <t>934587D07</t>
-  </si>
-  <si>
-    <t>940097P01</t>
-  </si>
-  <si>
-    <t>940097P03</t>
-  </si>
-  <si>
-    <t>940097P04</t>
-  </si>
-  <si>
-    <t>940097P05</t>
-  </si>
-  <si>
-    <t>940097P06</t>
-  </si>
-  <si>
-    <t>940097P07</t>
-  </si>
-  <si>
-    <t>940097P08</t>
-  </si>
-  <si>
-    <t>940097P02</t>
-  </si>
-  <si>
-    <t>940097A01</t>
-  </si>
-  <si>
-    <t>940097A02</t>
-  </si>
-  <si>
-    <t>940097A03</t>
-  </si>
-  <si>
-    <t>940097A04</t>
-  </si>
-  <si>
-    <t>940097D01</t>
-  </si>
-  <si>
-    <t>940097D05</t>
-  </si>
-  <si>
-    <t>940097D06</t>
-  </si>
-  <si>
-    <t>940097D04</t>
-  </si>
-  <si>
-    <t>940097D08</t>
-  </si>
-  <si>
-    <t>940097D03</t>
-  </si>
-  <si>
-    <t>940096P01</t>
-  </si>
-  <si>
-    <t>940096P03</t>
-  </si>
-  <si>
-    <t>940096P04</t>
-  </si>
-  <si>
-    <t>940096P05</t>
-  </si>
-  <si>
-    <t>940096P06</t>
-  </si>
-  <si>
-    <t>940096P07</t>
-  </si>
-  <si>
-    <t>940096P08</t>
-  </si>
-  <si>
-    <t>940096P02</t>
-  </si>
-  <si>
-    <t>940096A01</t>
-  </si>
-  <si>
-    <t>940096A02</t>
-  </si>
-  <si>
-    <t>940096A03</t>
-  </si>
-  <si>
-    <t>940096A04</t>
-  </si>
-  <si>
-    <t>940096D01</t>
-  </si>
-  <si>
-    <t>940096D05</t>
-  </si>
-  <si>
-    <t>940096D06</t>
-  </si>
-  <si>
-    <t>940096D04</t>
-  </si>
-  <si>
-    <t>940096D07</t>
-  </si>
-  <si>
-    <t>940096D03</t>
-  </si>
-  <si>
-    <t>940093P01</t>
-  </si>
-  <si>
-    <t>940093P03</t>
-  </si>
-  <si>
-    <t>940093P04</t>
-  </si>
-  <si>
-    <t>940093P05</t>
-  </si>
-  <si>
-    <t>940093P06</t>
-  </si>
-  <si>
-    <t>940093P07</t>
-  </si>
-  <si>
-    <t>940093P08</t>
-  </si>
-  <si>
-    <t>940093P02</t>
-  </si>
-  <si>
-    <t>940093A01</t>
-  </si>
-  <si>
-    <t>940093A02</t>
-  </si>
-  <si>
-    <t>940093A03</t>
-  </si>
-  <si>
-    <t>940093A04</t>
-  </si>
-  <si>
-    <t>940093D01</t>
-  </si>
-  <si>
-    <t>940093D05</t>
-  </si>
-  <si>
-    <t>940093D06</t>
-  </si>
-  <si>
-    <t>940093D04</t>
-  </si>
-  <si>
-    <t>940093D07</t>
-  </si>
-  <si>
-    <t>940093D03</t>
-  </si>
-  <si>
-    <t>943611P01</t>
-  </si>
-  <si>
-    <t>943611P11</t>
-  </si>
-  <si>
-    <t>943611P12</t>
-  </si>
-  <si>
-    <t>943611P13</t>
-  </si>
-  <si>
-    <t>943611P14</t>
-  </si>
-  <si>
-    <t>943611P15</t>
-  </si>
-  <si>
-    <t>943611P16</t>
-  </si>
-  <si>
-    <t>943611P02</t>
-  </si>
-  <si>
-    <t>943611A01</t>
-  </si>
-  <si>
-    <t>943611A02</t>
-  </si>
-  <si>
-    <t>943611A03</t>
-  </si>
-  <si>
-    <t>943611A04</t>
-  </si>
-  <si>
-    <t>943611D01</t>
-  </si>
-  <si>
-    <t>943611D02</t>
-  </si>
-  <si>
-    <t>943611D08</t>
-  </si>
-  <si>
-    <t>940094P01</t>
-  </si>
-  <si>
-    <t>940094P11</t>
-  </si>
-  <si>
-    <t>940094P12</t>
-  </si>
-  <si>
-    <t>940094P13</t>
-  </si>
-  <si>
-    <t>940094P14</t>
-  </si>
-  <si>
-    <t>940094P15</t>
-  </si>
-  <si>
-    <t>940094P16</t>
-  </si>
-  <si>
-    <t>940094P17</t>
-  </si>
-  <si>
-    <t>940094P18</t>
-  </si>
-  <si>
-    <t>940094P02</t>
-  </si>
-  <si>
-    <t>940094A01</t>
-  </si>
-  <si>
-    <t>940094A02</t>
-  </si>
-  <si>
-    <t>940094A03</t>
-  </si>
-  <si>
-    <t>940094A04</t>
-  </si>
-  <si>
-    <t>940094D01</t>
-  </si>
-  <si>
-    <t>940094D05</t>
-  </si>
-  <si>
-    <t>940094D06</t>
-  </si>
-  <si>
-    <t>940094D02</t>
-  </si>
-  <si>
-    <t>940094D07</t>
-  </si>
-  <si>
-    <t>940094D04</t>
-  </si>
-  <si>
-    <t>940095P01</t>
-  </si>
-  <si>
-    <t>940095P03</t>
-  </si>
-  <si>
-    <t>940095P04</t>
-  </si>
-  <si>
-    <t>940095P05</t>
-  </si>
-  <si>
-    <t>940095P06</t>
-  </si>
-  <si>
-    <t>940095P07</t>
-  </si>
-  <si>
-    <t>940095P08</t>
-  </si>
-  <si>
-    <t>940095P02</t>
-  </si>
-  <si>
-    <t>940095A01</t>
-  </si>
-  <si>
-    <t>940095A02</t>
-  </si>
-  <si>
-    <t>940095A03</t>
-  </si>
-  <si>
-    <t>940095A04</t>
-  </si>
-  <si>
-    <t>940095D01</t>
-  </si>
-  <si>
-    <t>940095D03</t>
-  </si>
-  <si>
-    <t>940095D04</t>
-  </si>
-  <si>
-    <t>940095D02</t>
-  </si>
-  <si>
-    <t>940095D07</t>
-  </si>
-  <si>
-    <t>940095D06</t>
-  </si>
-  <si>
-    <t>GCL Yamuna-9481219</t>
-  </si>
-  <si>
-    <t>GCL Tapi-9481659</t>
-  </si>
-  <si>
-    <t>GCL Sabarmati-9481661</t>
-  </si>
-  <si>
-    <t>GCL Ganga-9481697</t>
-  </si>
-  <si>
-    <t>AM Umang-9792058</t>
-  </si>
-  <si>
-    <t>AM Tarang-9832913</t>
-  </si>
-  <si>
-    <t>AM Kirti-9832925</t>
-  </si>
-  <si>
-    <t>GCL Narmadha-9481685</t>
-  </si>
-  <si>
-    <t>GCL Saraswati-9644500</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 940093P09</t>
+    <t>934587P19</t>
   </si>
 </sst>
 </file>
@@ -1241,31 +1241,31 @@
         <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="3" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.4">
@@ -1299,25 +1299,25 @@
         <v>107</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
@@ -1337,25 +1337,25 @@
         <v>108</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.4">
@@ -1375,25 +1375,25 @@
         <v>109</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
@@ -1413,25 +1413,25 @@
         <v>110</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
@@ -1451,25 +1451,25 @@
         <v>111</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
@@ -1489,25 +1489,25 @@
         <v>112</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.4">
@@ -1527,25 +1527,25 @@
         <v>113</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
@@ -1562,13 +1562,13 @@
         <v>93</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>46</v>
@@ -1600,13 +1600,13 @@
         <v>94</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>46</v>
@@ -1615,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>46</v>
@@ -1641,28 +1641,28 @@
         <v>95</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
@@ -1682,28 +1682,28 @@
         <v>96</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
@@ -1720,28 +1720,28 @@
         <v>97</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.4">
@@ -1758,28 +1758,28 @@
         <v>98</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
@@ -1796,28 +1796,28 @@
         <v>99</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
@@ -1837,28 +1837,28 @@
         <v>100</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
@@ -1875,10 +1875,10 @@
         <v>101</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>46</v>
@@ -1896,7 +1896,7 @@
         <v>46</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
@@ -1954,25 +1954,25 @@
         <v>102</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>46</v>
@@ -1992,25 +1992,25 @@
         <v>103</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>46</v>
@@ -2071,25 +2071,25 @@
         <v>104</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>46</v>
@@ -2381,7 +2381,7 @@
         <v>46</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>46</v>
@@ -2399,7 +2399,7 @@
         <v>46</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.4">
@@ -2536,25 +2536,25 @@
         <v>105</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>46</v>
@@ -2650,25 +2650,25 @@
         <v>106</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>46</v>
